--- a/aula14/BANCO/Base_BANCO_TABAJARA.xlsx
+++ b/aula14/BANCO/Base_BANCO_TABAJARA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu-my.sharepoint.com/personal/adenilson_sencarnaca_senacsp_edu_br/Documents/UC06 -  Desenvolver algoritmos/aula14/BANCO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_2B59D2BFD380D2F62222BC92461510344D07F204" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF360C5F-D6C0-4A5C-B465-1BAB82657DF1}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_2B59D2BFD3B0D1653DC3DDF050A208F040E5FB67" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC2A0EE3-D57C-492E-BF11-D57A02915602}"/>
   <bookViews>
-    <workbookView xWindow="4005" yWindow="3825" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="4725" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>nome_cliente</t>
   </si>
@@ -44,6 +44,48 @@
   </si>
   <si>
     <t>saque</t>
+  </si>
+  <si>
+    <t>Adenilson</t>
+  </si>
+  <si>
+    <t>Corrente</t>
+  </si>
+  <si>
+    <t>123.456.789-00</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Poupança</t>
+  </si>
+  <si>
+    <t>Micael</t>
+  </si>
+  <si>
+    <t>Luiz</t>
+  </si>
+  <si>
+    <t>Trabalho</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>Bernardo</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Salario</t>
+  </si>
+  <si>
+    <t>55566677733</t>
   </si>
 </sst>
 </file>
@@ -383,13 +425,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -418,6 +457,234 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>11122233355</v>
+      </c>
+      <c r="E3">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>33322255566</v>
+      </c>
+      <c r="E4">
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>99955544477</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>11144499977</v>
+      </c>
+      <c r="E6">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>55533344477</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>24</v>
+      </c>
+      <c r="D8">
+        <v>44499933311</v>
+      </c>
+      <c r="E8">
+        <v>23</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C9">
+        <v>25</v>
+      </c>
+      <c r="D9">
+        <v>22288899977</v>
+      </c>
+      <c r="E9">
+        <v>24</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10">
+        <v>25</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aula14/BANCO/Base_BANCO_TABAJARA.xlsx
+++ b/aula14/BANCO/Base_BANCO_TABAJARA.xlsx
@@ -1,109 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu-my.sharepoint.com/personal/adenilson_sencarnaca_senacsp_edu_br/Documents/UC06 -  Desenvolver algoritmos/aula14/BANCO/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_2B59D2BFD3B0D1653DC3DDF050A208F040E5FB67" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC2A0EE3-D57C-492E-BF11-D57A02915602}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4725" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
-  <si>
-    <t>nome_cliente</t>
-  </si>
-  <si>
-    <t>tipo_conta</t>
-  </si>
-  <si>
-    <t>numero_conta</t>
-  </si>
-  <si>
-    <t>cpf</t>
-  </si>
-  <si>
-    <t>agencia</t>
-  </si>
-  <si>
-    <t>extrato_bancario</t>
-  </si>
-  <si>
-    <t>deposito</t>
-  </si>
-  <si>
-    <t>saque</t>
-  </si>
-  <si>
-    <t>Adenilson</t>
-  </si>
-  <si>
-    <t>Corrente</t>
-  </si>
-  <si>
-    <t>123.456.789-00</t>
-  </si>
-  <si>
-    <t>Daniel</t>
-  </si>
-  <si>
-    <t>Poupança</t>
-  </si>
-  <si>
-    <t>Micael</t>
-  </si>
-  <si>
-    <t>Luiz</t>
-  </si>
-  <si>
-    <t>Trabalho</t>
-  </si>
-  <si>
-    <t>Pedro</t>
-  </si>
-  <si>
-    <t>Bernardo</t>
-  </si>
-  <si>
-    <t>Eduardo</t>
-  </si>
-  <si>
-    <t>Sales</t>
-  </si>
-  <si>
-    <t>Salario</t>
-  </si>
-  <si>
-    <t>55566677733</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -122,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -424,264 +408,383 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="4" width="14" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>nome_cliente</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tipo_conta</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>numero_conta</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>cpf</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>agencia</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>extrato_bancario</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>deposito</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>saque</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Adenilson</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Corrente</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>123.456.789-00</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Poupança</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>19</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>11122233355</v>
       </c>
-      <c r="E3">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
+      <c r="E3" t="n">
+        <v>401</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Micael</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Corrente</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>20</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>33322255566</v>
       </c>
-      <c r="E4">
-        <v>19</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5">
+      <c r="E4" t="n">
+        <v>402</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Luiz</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Trabalho</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>21</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>99955544477</v>
       </c>
-      <c r="E5">
-        <v>20</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
+      <c r="E5" t="n">
+        <v>403</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Trabalho</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>22</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>11144499977</v>
       </c>
-      <c r="E6">
-        <v>21</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7">
+      <c r="E6" t="n">
+        <v>404</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bernardo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Corrente</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>23</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>55533344477</v>
       </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8">
+      <c r="E7" t="n">
+        <v>405</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Poupança</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>24</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>44499933311</v>
       </c>
-      <c r="E8">
-        <v>23</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C9">
+      <c r="E8" t="n">
+        <v>406</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
         <v>25</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>22288899977</v>
       </c>
-      <c r="E9">
-        <v>24</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10">
+      <c r="E9" t="n">
+        <v>407</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Salario</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>26</v>
       </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10">
-        <v>25</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>55566677733</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>408</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Poupança</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>55566644499</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>26</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Corrente</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>28</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>11122211199</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>410</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/aula14/BANCO/Base_BANCO_TABAJARA.xlsx
+++ b/aula14/BANCO/Base_BANCO_TABAJARA.xlsx
@@ -513,7 +513,7 @@
         <v>401</v>
       </c>
       <c r="F3" t="n">
-        <v>400</v>
+        <v>318</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -545,7 +545,7 @@
         <v>402</v>
       </c>
       <c r="F4" t="n">
-        <v>447</v>
+        <v>392.442</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -577,7 +577,7 @@
         <v>403</v>
       </c>
       <c r="F5" t="n">
-        <v>807</v>
+        <v>681.2646</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
